--- a/data/processed/indicadores_ECO_SIEPAC.xlsx
+++ b/data/processed/indicadores_ECO_SIEPAC.xlsx
@@ -672,17 +672,17 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>Consumo Final Industrial (kWh) ÷ Valor Agregado Industrial (USD constantes 2015)</t>
+          <t>Consumo Final Industrial (kWh) ÷ Valor Agregado Manufacturero (USD constantes 2015)</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>SIELAC-OLADE (consumo industrial); CEPALSTAT ODS 9.2.1 × Banco Mundial (VAI)</t>
+          <t>SIELAC-OLADE (consumo industrial); CEPALSTAT ODS 9.2.1 × Banco Mundial (VAM)</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>El VAI en USD ya fue calculado en el ETL como VAI%% × PIB real.</t>
+          <t>El VAM en USD ya fue calculado en el ETL como VAM%% (ODS 9.2.1) × PIB real.</t>
         </is>
       </c>
     </row>
@@ -769,12 +769,12 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>CEPAL-SIECA (serie histórica); imputación CAGR para años faltantes documentada en el ETL</t>
+          <t>CEPAL-SIECA (serie histórica); cálculo CAGR documentado en el ETL</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>En USD corrientes del año bajo análisis (no constantes). Las celdas sombreadas en amarillo son valores imputados vía CAGR de la serie histórica 2015+ (ver Datos_Base, columna tarifa_fuente_dato).</t>
+          <t>En USD corrientes del año bajo análisis (no constantes). Las celdas sombreadas en amarillo son valores calculados mediante CAGR de la serie histórica 2015+ (ver Datos_Base, columna tarifa_fuente_dato).</t>
         </is>
       </c>
     </row>
@@ -4152,7 +4152,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Fórmula: Consumo Final Industrial (kWh) ÷ Valor Agregado Industrial (USD constantes 2015)</t>
+          <t>Fórmula: Consumo Final Industrial (kWh) ÷ Valor Agregado Manufacturero (USD constantes 2015)</t>
         </is>
       </c>
     </row>
@@ -5192,14 +5192,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Sin agregado regional: la fuente no publica la energía regulada vendida (MWh) por país para ponderar la tarifa.</t>
+          <t>Agregado regional no definido: la razón de sumas requiere energía regulada vendida (MWh) por país y año.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Celdas en amarillo: valores imputados vía CAGR (no observados). Detalle en Datos_Base, columna tarifa_fuente_dato.</t>
+          <t>Celdas en amarillo: valores calculados mediante CAGR. Detalle en Datos_Base, columna tarifa_fuente_dato.</t>
         </is>
       </c>
     </row>
